--- a/documents/PAPER1_ARTICLE_TRACKER.xlsx
+++ b/documents/PAPER1_ARTICLE_TRACKER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/remyndayizeye/Desktop/Data Science Projects/vcamon-app/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CA3B717-F9E3-214D-9098-329318D7E630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{91853D92-F99E-6E4B-9DD7-57E5F4DA5F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{57F2BC60-CB27-4A4B-95CF-FF5B218B161D}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>search_date</t>
   </si>
@@ -116,6 +116,18 @@
   </si>
   <si>
     <t>notes</t>
+  </si>
+  <si>
+    <t>PUBMED</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>((("Syphilis"[Mesh] OR syphilis[tiab]) AND ("Partner notification"[Mesh] OR "partner services"[tiab] OR "contact tracing"[tiab] OR "disease intervention specialist"[tiab] OR "case investigation"[tiab])) AND "Syphilis/prevention and control"[MAJR]) AND "Syphilis/epidemiology"[MeSH]</t>
+  </si>
+  <si>
+    <t>English, Humans</t>
   </si>
 </sst>
 </file>
@@ -599,8 +611,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -976,8 +989,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80AA290-C68C-8042-987C-CE858F99A3B8}">
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="11" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1075,6 +1091,26 @@
       </c>
       <c r="AF1" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
